--- a/core/data/events.xlsx
+++ b/core/data/events.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="305">
   <si>
     <t>شماره ماه</t>
   </si>
@@ -234,12 +234,6 @@
     <t>اربعین حسینی</t>
   </si>
   <si>
-    <t>روز خبرنگار</t>
-  </si>
-  <si>
-    <t>رحلت رسول اکرم؛شهادت امام حسن مجتبی (ع)</t>
-  </si>
-  <si>
     <t>شهادت امام رضا (ع)</t>
   </si>
   <si>
@@ -252,39 +246,15 @@
     <t>روز جهانی عکاسی</t>
   </si>
   <si>
-    <t>شهادت امام حسن عسکری (ع)</t>
-  </si>
-  <si>
-    <t>روز بزرگداشت ابوعلی سینا و روز پزشک</t>
-  </si>
-  <si>
-    <t>آغاز هفته دولت</t>
-  </si>
-  <si>
-    <t>میلاد رسول اکرم به روایت اهل سنت</t>
-  </si>
-  <si>
     <t>زادروز کوروش بزرگ | شهریور روز،جشن شهریورگان</t>
   </si>
   <si>
     <t>روز بزرگداشت محمدبن زکریای رازی و روز داروساز</t>
   </si>
   <si>
-    <t>انفجار در دفتر نخست‌وزیری جمهوری اسلامی ایران، روز مبارزه با تروریسم</t>
-  </si>
-  <si>
-    <t>میلاد رسول اکرم و امام جعفر صادق (ع)</t>
-  </si>
-  <si>
     <t>روز ملی صنعت چاپ</t>
   </si>
   <si>
-    <t>سالروز شهادت رئیسعلی دلواری، سردار بزرگ میهن و فرمانده قیام جنوب علیه اشغالگران انگلیسی</t>
-  </si>
-  <si>
-    <t>روز بزرگداشت ابوریحان بیرونی</t>
-  </si>
-  <si>
     <t>روز جهانی پیشگیری از خودکشی</t>
   </si>
   <si>
@@ -294,33 +264,18 @@
     <t>روز سینما</t>
   </si>
   <si>
-    <t>روز شعر و ادب پارسی و روز بزرگداشت استاد شهریار</t>
-  </si>
-  <si>
     <t>ولادت امام حسن عسکری (ع)</t>
   </si>
   <si>
     <t>روز جهانی صلح</t>
   </si>
   <si>
-    <t>آغاز هفته دفاع مقدس</t>
-  </si>
-  <si>
     <t>وفات حضرت معصومه (س)</t>
   </si>
   <si>
-    <t>آغاز حمله مغول به ایران در پاییز 598 خورشیدی</t>
-  </si>
-  <si>
-    <t>روز گرامیداشت سربازان وطن</t>
-  </si>
-  <si>
     <t>روز جهانی جهانگردی</t>
   </si>
   <si>
-    <t>روز آتش نشانی و ایمنی | سقوط هواپیمای حامل جمعی از فرماندهان جنگ (کلاهدوز، نامجو، فلاحی، فکوری، جهان آرا) در سال 1360 | روز بزرگداشت شمس تبریزی</t>
-  </si>
-  <si>
     <t>روزبزرگداشت مولوی</t>
   </si>
   <si>
@@ -330,21 +285,12 @@
     <t>روز جهانی ناشنوایان | روز جهانی ترجمه و مترجم</t>
   </si>
   <si>
-    <t>مهر روز،جشن مهرگان</t>
-  </si>
-  <si>
     <t>آغاز هفته جهانی فضا</t>
   </si>
   <si>
-    <t>روز جهانی معلم</t>
-  </si>
-  <si>
     <t>روز دامپزشکی</t>
   </si>
   <si>
-    <t>روز ملی کودک</t>
-  </si>
-  <si>
     <t>روز جهانی پست</t>
   </si>
   <si>
@@ -363,42 +309,18 @@
     <t>روز جهانی استاندارد</t>
   </si>
   <si>
-    <t>روز جهانی عصای سفید</t>
-  </si>
-  <si>
     <t>روز جهانی غذا</t>
   </si>
   <si>
     <t>روز جهانی ریشه کنی فقر</t>
   </si>
   <si>
-    <t>ولادت حضرت زینب (س) و روز پرستار و بهورز</t>
-  </si>
-  <si>
     <t>روز تربیت بدنی و ورزش</t>
   </si>
   <si>
     <t>زادروز ستارخان ملقب به سردار ملی و از سرداران جنبش مشروطه ایران</t>
   </si>
   <si>
-    <t>روز ملی کوهنورد</t>
-  </si>
-  <si>
-    <t>روز آمار و برنامه ریزی | روز بزرگداشت ابوالفضل بیهقی، تاریخ‌نگار و نویسنده ایرانی</t>
-  </si>
-  <si>
-    <t>سالروز ورود کوروش بزرگ به بابل در سال 539 پیش از میلاد</t>
-  </si>
-  <si>
-    <t>روز ملی محیط بان</t>
-  </si>
-  <si>
-    <t>آبان روز، جشن آبانگان</t>
-  </si>
-  <si>
-    <t>روز ملّی مازندران</t>
-  </si>
-  <si>
     <t>جشن میانه پاییز</t>
   </si>
   <si>
@@ -411,9 +333,6 @@
     <t>روز جهانی دیابت</t>
   </si>
   <si>
-    <t>روز کتاب و کتابخوانی</t>
-  </si>
-  <si>
     <t>روز جهانی دانش آموز</t>
   </si>
   <si>
@@ -423,24 +342,12 @@
     <t>روز جهانی کودک</t>
   </si>
   <si>
-    <t>آذر جشن</t>
-  </si>
-  <si>
     <t>روز جهانی مبارزه با خشونت علیه زنان</t>
   </si>
   <si>
-    <t>روز بسیج مستضعفان</t>
-  </si>
-  <si>
-    <t>سالروز عملیات مروارید و روز نیروی دریایی ارتش</t>
-  </si>
-  <si>
     <t>جشن آذرگان ،آذر روز</t>
   </si>
   <si>
-    <t>ولادت حضرت فاطمه زهرا (س) و روز مادر</t>
-  </si>
-  <si>
     <t>روز جهانی ایدز</t>
   </si>
   <si>
@@ -820,19 +727,231 @@
   </si>
   <si>
     <t>سالروز صدور فرمان مشروطیت | روز حقوق بشر اسلامی و کرامت انسانی</t>
+  </si>
+  <si>
+    <t>روز خبرنگار | سالروز شهادت محمود صارمی</t>
+  </si>
+  <si>
+    <t>بزرگداشت شهدای مدافع حرم</t>
+  </si>
+  <si>
+    <t>رحلت رسول اکرم | شهادت امام حسن مجتبی (ع)</t>
+  </si>
+  <si>
+    <t>روز حمایت از صنایع کوچک</t>
+  </si>
+  <si>
+    <t>روز تشکل ها و مشارکت های اجتماعی</t>
+  </si>
+  <si>
+    <t>روز مقاومت اسلامی</t>
+  </si>
+  <si>
+    <t>بازگشت آزادگان به میهن اسلامی</t>
+  </si>
+  <si>
+    <t>شهادت امام حسن عسکری (ع) | آغاز امامت حضرت ولیعصر (عج)</t>
+  </si>
+  <si>
+    <t>روز جهانی مسجد</t>
+  </si>
+  <si>
+    <t>بزرگداشت علامه مجلسی</t>
+  </si>
+  <si>
+    <t>روز صنعت دفاعی | روز عسل</t>
+  </si>
+  <si>
+    <t>روز بزرگداشت ابوعلی سینا | روز پزشک | روز همدان</t>
+  </si>
+  <si>
+    <t>آغاز هفته دولت | شهادت سید علی اندرزگو</t>
+  </si>
+  <si>
+    <t>میلاد رسول اکرم به روایت اهل سنت | آغاز هفته وحدت</t>
+  </si>
+  <si>
+    <t>اشغال ایران توسط متفقین</t>
+  </si>
+  <si>
+    <t>انفجار در دفتر نخست‌وزیری جمهوری اسلامی ایران | روز مبارزه با تروریسم | شهادت شهیدان رجایی و باهنر</t>
+  </si>
+  <si>
+    <t>میلاد رسول اکرم و امام جعفر صادق (ع) | روز اخلاق و مهرورزی</t>
+  </si>
+  <si>
+    <t>روز بانکداری اسلامی | سالروز تصویب قانون عملیات بانکی بدون ربا | روز تشکیل قرارگاه پدافند هوایی خاتم الانبیا</t>
+  </si>
+  <si>
+    <t>سالروز شهادت رئیسعلی دلواری، سردار بزرگ میهن و فرمانده قیام جنوب علیه اشغالگران انگلیسی | روز ملی مبارزه با استعمار انگلیس | روز بهورز</t>
+  </si>
+  <si>
+    <t>شهادت آیت الله قدوسی و سرتیپ وحید دستجردی</t>
+  </si>
+  <si>
+    <t>روز بزرگداشت ابوریحان بیرونی | روز تعاون | روز مردم شناسی | روز علوم پایه | سالروز زلزله فردوس در سال 1347 | روز حرکت‌های جهادی و امداد مردمی</t>
+  </si>
+  <si>
+    <t>روز قم</t>
+  </si>
+  <si>
+    <t>قیام 17 شهریور</t>
+  </si>
+  <si>
+    <t>وفات آیت الله سید محمود طالقانی</t>
+  </si>
+  <si>
+    <t>شهادت آیت الله مدنی</t>
+  </si>
+  <si>
+    <t>روز شعر و ادب پارسی | روز بزرگداشت استاد شهریار</t>
+  </si>
+  <si>
+    <t>روز خرما | روز ملی کفاش | روز ملی صنعت کفش و چرم</t>
+  </si>
+  <si>
+    <t>ولادت حضرت عبدالعظیم حسنی (ع)</t>
+  </si>
+  <si>
+    <t>روز فوریت های پزشکی (اورژانس)</t>
+  </si>
+  <si>
+    <t>آغاز هفته دفاع مقدس | آغاز جنگ تحمیلی</t>
+  </si>
+  <si>
+    <t>آغاز حمله مغول به ایران در پاییز 598 خورشیدی | روز پرچم</t>
+  </si>
+  <si>
+    <t>بزرگداشت شهدای منا</t>
+  </si>
+  <si>
+    <t>روز گرامیداشت سربازان وطن | روز سرباز</t>
+  </si>
+  <si>
+    <t>شکست حصر آبادان</t>
+  </si>
+  <si>
+    <t>روز آتش نشانی و ایمنی | سقوط هواپیمای حامل جمعی از فرماندهان جنگ (شهادت سرداران کلاهدوز، نامجو، فلاحی، فکوری، جهان آرا) در سال 1360 | بزرگداشت فرماندهان شهید دفاع مقدس | روز بزرگداشت شمس تبریزی</t>
+  </si>
+  <si>
+    <t>روز جهانی دریانوردی</t>
+  </si>
+  <si>
+    <t>روز همبستگی و همدردی با کودکان و نوجوانان فلسطینی</t>
+  </si>
+  <si>
+    <t>مهر روز،جشن مهرگان |  روز ملي نخبگان</t>
+  </si>
+  <si>
+    <t>روز جهانی معلم | روز نیروی انتظامی</t>
+  </si>
+  <si>
+    <t>هجرت امام خمینی از عراق به پاریس</t>
+  </si>
+  <si>
+    <t>روز ملی روستا و عشایر | روز جهانی حماسه فلسطین</t>
+  </si>
+  <si>
+    <t>روز جهانی عصای سفید (نابینایان)</t>
+  </si>
+  <si>
+    <t>شهادت آیت الله اشرفی اصفهانی</t>
+  </si>
+  <si>
+    <t>ولادت حضرت زینب (س) | روز پرستار و بهورز</t>
+  </si>
+  <si>
+    <t>روز ملی پارالمپیک | روز پیوند اولیا و مربیان | روز صنعت آسانسور و پله برقی</t>
+  </si>
+  <si>
+    <t>روز ملی کوهنورد | روز صادرات</t>
+  </si>
+  <si>
+    <t>روز ملی آمار و برنامه ریزی | روز بزرگداشت ابوالفضل بیهقی، تاریخ‌نگار و نویسنده ایرانی</t>
+  </si>
+  <si>
+    <t>اعتراض امام خمینی علیه پذیرش کاپیتولاسیون</t>
+  </si>
+  <si>
+    <t>روز ملی زعفران</t>
+  </si>
+  <si>
+    <t>سالروز ورود کوروش بزرگ به بابل در سال 539 پیش از میلاد | روز انار</t>
+  </si>
+  <si>
+    <t>روز ملی محیط بان | شهادت محمد حسین فهمیده | روز نوجوان | روز بسیج دانش‌آموزی | روز پدافند غیرعامل</t>
+  </si>
+  <si>
+    <t>آبان روز، جشن آبانگان | شهادت آیت الله قاضی طباطبایی</t>
+  </si>
+  <si>
+    <t>تسخیر سفارت آمریکا | روز ملی مبارزه با استکبار جهانی | روز دانش آموز | تبعید امام خمینی از ایران به ترکیه</t>
+  </si>
+  <si>
+    <t>روز ملّی مازندران | روز فرهنگ عمومی</t>
+  </si>
+  <si>
+    <t>روز جهانی علم در خدمت صلح و توسعه</t>
+  </si>
+  <si>
+    <t>روز ملی هوا ـ فضا</t>
+  </si>
+  <si>
+    <t>روز کتاب، کتابخوانی و کتابدار | روز بزرگداشت آیت الله علامه سید محمد حسین طباطبایی</t>
+  </si>
+  <si>
+    <t>روز ملی صنعت نوشت افزار</t>
+  </si>
+  <si>
+    <t>سالروز آزادسازی سوسنگرد</t>
+  </si>
+  <si>
+    <t>روز جهانی حکمت و فلسفه</t>
+  </si>
+  <si>
+    <t>وز ملی حکمت و فلسفه | بزرگداشت ابونصر فارابی | روز قهرمان ملی</t>
+  </si>
+  <si>
+    <t>آذر جشن | روز ملی اصفهان | روز ملی صنعت سرب و روی</t>
+  </si>
+  <si>
+    <t>سالروز وفات حضرت ام البنین (س) | روز تکریم مادران و همسران شهدا</t>
+  </si>
+  <si>
+    <t>روز ملی زیتون</t>
+  </si>
+  <si>
+    <t>روز جهانی درخت زیتون</t>
+  </si>
+  <si>
+    <t>روز بسیج مستضعفان | سالروز قیام مردم گرگان</t>
+  </si>
+  <si>
+    <t>سالروز عملیات مروارید | روز نیروی دریایی ارتش | روز نوآوری و فناوری ایران ساخت</t>
+  </si>
+  <si>
+    <t>روز بین‌المللی همبستگی با مردم فلسطین</t>
+  </si>
+  <si>
+    <t>ولادت حضرت فاطمه زهرا (س) | روز مادر</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF091E42"/>
+      <name val="Shabnam"/>
     </font>
   </fonts>
   <fills count="2">
@@ -855,11 +974,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1140,15 +1260,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D265"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D304"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
     <col min="2" max="3" width="12.5703125" customWidth="1"/>
     <col min="4" max="4" width="45.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1162,7 +1282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1176,7 +1296,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1190,7 +1310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1204,7 +1324,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1215,10 +1335,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1229,10 +1349,10 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1246,7 +1366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1260,7 +1380,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1274,7 +1394,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1288,7 +1408,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1302,7 +1422,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1316,7 +1436,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1330,7 +1450,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1344,7 +1464,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1355,10 +1475,10 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1369,10 +1489,10 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1383,10 +1503,10 @@
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1400,7 +1520,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1414,7 +1534,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1425,10 +1545,10 @@
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1439,10 +1559,10 @@
         <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1456,7 +1576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1470,7 +1590,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -1484,7 +1604,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1495,10 +1615,10 @@
         <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -1512,7 +1632,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1526,7 +1646,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -1537,10 +1657,10 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -1551,10 +1671,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1568,7 +1688,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -1579,10 +1699,10 @@
         <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -1593,10 +1713,10 @@
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -1607,10 +1727,10 @@
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1621,10 +1741,10 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -1635,10 +1755,10 @@
         <v>5</v>
       </c>
       <c r="D35" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -1652,7 +1772,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -1663,10 +1783,10 @@
         <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -1677,10 +1797,10 @@
         <v>26</v>
       </c>
       <c r="D38" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -1694,7 +1814,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -1708,7 +1828,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1719,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="D41" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -1733,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -1750,7 +1870,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
         <v>3</v>
       </c>
@@ -1761,10 +1881,10 @@
         <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
         <v>3</v>
       </c>
@@ -1775,10 +1895,10 @@
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1792,7 +1912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1806,7 +1926,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
         <v>3</v>
       </c>
@@ -1817,10 +1937,10 @@
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>3</v>
       </c>
@@ -1831,10 +1951,10 @@
         <v>19</v>
       </c>
       <c r="D49" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
         <v>3</v>
       </c>
@@ -1845,10 +1965,10 @@
         <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -1859,10 +1979,10 @@
         <v>22</v>
       </c>
       <c r="D51" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1876,7 +1996,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>3</v>
       </c>
@@ -1887,10 +2007,10 @@
         <v>24</v>
       </c>
       <c r="D53" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>3</v>
       </c>
@@ -1901,10 +2021,10 @@
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -1918,7 +2038,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -1932,7 +2052,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>3</v>
       </c>
@@ -1946,7 +2066,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -1960,7 +2080,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -1971,10 +2091,10 @@
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>3</v>
       </c>
@@ -1985,10 +2105,10 @@
         <v>30</v>
       </c>
       <c r="D60" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>3</v>
       </c>
@@ -1999,10 +2119,10 @@
         <v>31</v>
       </c>
       <c r="D61" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>3</v>
       </c>
@@ -2016,7 +2136,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>3</v>
       </c>
@@ -2030,7 +2150,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>3</v>
       </c>
@@ -2044,7 +2164,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -2058,7 +2178,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>3</v>
       </c>
@@ -2072,7 +2192,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -2083,10 +2203,10 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
         <v>3</v>
       </c>
@@ -2097,10 +2217,10 @@
         <v>5</v>
       </c>
       <c r="D68" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
         <v>3</v>
       </c>
@@ -2114,7 +2234,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -2128,7 +2248,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
         <v>3</v>
       </c>
@@ -2139,10 +2259,10 @@
         <v>7</v>
       </c>
       <c r="D71" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
         <v>3</v>
       </c>
@@ -2153,10 +2273,10 @@
         <v>8</v>
       </c>
       <c r="D72" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -2170,7 +2290,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>5</v>
       </c>
@@ -2184,7 +2304,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
         <v>3</v>
       </c>
@@ -2198,7 +2318,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -2212,7 +2332,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
         <v>3</v>
       </c>
@@ -2226,7 +2346,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -2240,7 +2360,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
         <v>5</v>
       </c>
@@ -2254,7 +2374,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
         <v>3</v>
       </c>
@@ -2265,10 +2385,10 @@
         <v>20</v>
       </c>
       <c r="D80" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
         <v>5</v>
       </c>
@@ -2279,10 +2399,10 @@
         <v>24</v>
       </c>
       <c r="D81" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
         <v>7</v>
       </c>
@@ -2296,7 +2416,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -2307,10 +2427,10 @@
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
         <v>7</v>
       </c>
@@ -2324,7 +2444,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
         <v>7</v>
       </c>
@@ -2338,7 +2458,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
         <v>3</v>
       </c>
@@ -2349,10 +2469,10 @@
         <v>23</v>
       </c>
       <c r="D86" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
         <v>3</v>
       </c>
@@ -2366,7 +2486,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
         <v>7</v>
       </c>
@@ -2380,7 +2500,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
         <v>5</v>
       </c>
@@ -2391,10 +2511,10 @@
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
         <v>3</v>
       </c>
@@ -2405,10 +2525,10 @@
         <v>26</v>
       </c>
       <c r="D90" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
         <v>7</v>
       </c>
@@ -2422,7 +2542,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
         <v>5</v>
       </c>
@@ -2433,10 +2553,10 @@
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
         <v>3</v>
       </c>
@@ -2447,10 +2567,10 @@
         <v>27</v>
       </c>
       <c r="D93" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
         <v>3</v>
       </c>
@@ -2461,10 +2581,10 @@
         <v>29</v>
       </c>
       <c r="D94" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
         <v>3</v>
       </c>
@@ -2475,10 +2595,10 @@
         <v>30</v>
       </c>
       <c r="D95" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
         <v>7</v>
       </c>
@@ -2489,10 +2609,10 @@
         <v>20</v>
       </c>
       <c r="D96" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
         <v>3</v>
       </c>
@@ -2503,10 +2623,10 @@
         <v>31</v>
       </c>
       <c r="D97" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
         <v>3</v>
       </c>
@@ -2517,10 +2637,10 @@
         <v>1</v>
       </c>
       <c r="D98" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
         <v>5</v>
       </c>
@@ -2534,7 +2654,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
         <v>5</v>
       </c>
@@ -2548,7 +2668,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
         <v>7</v>
       </c>
@@ -2562,7 +2682,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
         <v>3</v>
       </c>
@@ -2573,10 +2693,10 @@
         <v>5</v>
       </c>
       <c r="D102" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
         <v>5</v>
       </c>
@@ -2590,7 +2710,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
         <v>3</v>
       </c>
@@ -2601,10 +2721,10 @@
         <v>7</v>
       </c>
       <c r="D104" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
       <c r="A105" t="s">
         <v>3</v>
       </c>
@@ -2618,7 +2738,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
         <v>3</v>
       </c>
@@ -2629,10 +2749,10 @@
         <v>10</v>
       </c>
       <c r="D106" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
       <c r="A107" t="s">
         <v>3</v>
       </c>
@@ -2643,10 +2763,10 @@
         <v>11</v>
       </c>
       <c r="D107" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
         <v>3</v>
       </c>
@@ -2657,10 +2777,10 @@
         <v>12</v>
       </c>
       <c r="D108" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
         <v>3</v>
       </c>
@@ -2674,7 +2794,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
         <v>3</v>
       </c>
@@ -2688,7 +2808,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
         <v>3</v>
       </c>
@@ -2702,7 +2822,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
         <v>3</v>
       </c>
@@ -2713,10 +2833,10 @@
         <v>16</v>
       </c>
       <c r="D112" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
       <c r="A113" t="s">
         <v>3</v>
       </c>
@@ -2727,10 +2847,10 @@
         <v>18</v>
       </c>
       <c r="D113" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
       <c r="A114" t="s">
         <v>3</v>
       </c>
@@ -2741,10 +2861,10 @@
         <v>21</v>
       </c>
       <c r="D114" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
       <c r="A115" t="s">
         <v>3</v>
       </c>
@@ -2758,7 +2878,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4">
       <c r="A116" t="s">
         <v>3</v>
       </c>
@@ -2769,10 +2889,10 @@
         <v>23</v>
       </c>
       <c r="D116" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
       <c r="A117" t="s">
         <v>3</v>
       </c>
@@ -2786,7 +2906,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4">
       <c r="A118" t="s">
         <v>3</v>
       </c>
@@ -2797,10 +2917,10 @@
         <v>26</v>
       </c>
       <c r="D118" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
       <c r="A119" t="s">
         <v>3</v>
       </c>
@@ -2814,7 +2934,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4">
       <c r="A120" t="s">
         <v>3</v>
       </c>
@@ -2825,10 +2945,10 @@
         <v>30</v>
       </c>
       <c r="D120" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -2839,10 +2959,10 @@
         <v>7</v>
       </c>
       <c r="D121" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
       <c r="A122" t="s">
         <v>3</v>
       </c>
@@ -2853,10 +2973,10 @@
         <v>4</v>
       </c>
       <c r="D122" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
       <c r="A123" t="s">
         <v>3</v>
       </c>
@@ -2867,10 +2987,10 @@
         <v>5</v>
       </c>
       <c r="D123" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
       <c r="A124" t="s">
         <v>3</v>
       </c>
@@ -2881,10 +3001,10 @@
         <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -2898,7 +3018,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4">
       <c r="A126" t="s">
         <v>3</v>
       </c>
@@ -2909,10 +3029,10 @@
         <v>8</v>
       </c>
       <c r="D126" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
       <c r="A127" t="s">
         <v>3</v>
       </c>
@@ -2923,10 +3043,10 @@
         <v>9</v>
       </c>
       <c r="D127" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
       <c r="A128" t="s">
         <v>3</v>
       </c>
@@ -2940,7 +3060,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4">
       <c r="A129" t="s">
         <v>7</v>
       </c>
@@ -2954,7 +3074,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4">
       <c r="A130" t="s">
         <v>5</v>
       </c>
@@ -2968,7 +3088,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4">
       <c r="A131" t="s">
         <v>3</v>
       </c>
@@ -2979,10 +3099,10 @@
         <v>14</v>
       </c>
       <c r="D131" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
       <c r="A132" t="s">
         <v>3</v>
       </c>
@@ -2993,24 +3113,24 @@
         <v>17</v>
       </c>
       <c r="D132" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B133">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C133">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D133" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="15.75" customHeight="1">
       <c r="A134" t="s">
         <v>5</v>
       </c>
@@ -3018,55 +3138,55 @@
         <v>2</v>
       </c>
       <c r="C134">
+        <v>28</v>
+      </c>
+      <c r="D134" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A135" t="s">
+        <v>3</v>
+      </c>
+      <c r="B135">
+        <v>5</v>
+      </c>
+      <c r="C135">
+        <v>21</v>
+      </c>
+      <c r="D135" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A136" t="s">
+        <v>3</v>
+      </c>
+      <c r="B136">
+        <v>5</v>
+      </c>
+      <c r="C136">
+        <v>22</v>
+      </c>
+      <c r="D136" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" t="s">
+        <v>5</v>
+      </c>
+      <c r="B137">
+        <v>2</v>
+      </c>
+      <c r="C137">
         <v>30</v>
       </c>
-      <c r="D134" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>7</v>
-      </c>
-      <c r="B135">
-        <v>8</v>
-      </c>
-      <c r="C135">
-        <v>13</v>
-      </c>
-      <c r="D135" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>5</v>
-      </c>
-      <c r="B136">
-        <v>3</v>
-      </c>
-      <c r="C136">
-        <v>1</v>
-      </c>
-      <c r="D136" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>3</v>
-      </c>
-      <c r="B137">
-        <v>5</v>
-      </c>
-      <c r="C137">
-        <v>28</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
       <c r="A138" t="s">
         <v>7</v>
       </c>
@@ -3074,139 +3194,139 @@
         <v>8</v>
       </c>
       <c r="C138">
+        <v>13</v>
+      </c>
+      <c r="D138" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" t="s">
+        <v>5</v>
+      </c>
+      <c r="B139">
+        <v>3</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+      <c r="D139" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" t="s">
+        <v>3</v>
+      </c>
+      <c r="B140">
+        <v>5</v>
+      </c>
+      <c r="C140">
+        <v>23</v>
+      </c>
+      <c r="D140" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" t="s">
+        <v>3</v>
+      </c>
+      <c r="B141">
+        <v>5</v>
+      </c>
+      <c r="C141">
+        <v>26</v>
+      </c>
+      <c r="D141" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="30">
+      <c r="A142" t="s">
+        <v>3</v>
+      </c>
+      <c r="B142">
+        <v>5</v>
+      </c>
+      <c r="C142">
+        <v>28</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" t="s">
+        <v>7</v>
+      </c>
+      <c r="B143">
+        <v>8</v>
+      </c>
+      <c r="C143">
         <v>19</v>
       </c>
-      <c r="D138" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>5</v>
-      </c>
-      <c r="B139">
-        <v>3</v>
-      </c>
-      <c r="C139">
+      <c r="D143" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" t="s">
+        <v>7</v>
+      </c>
+      <c r="B144">
         <v>8</v>
       </c>
-      <c r="D139" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>3</v>
-      </c>
-      <c r="B140">
-        <v>6</v>
-      </c>
-      <c r="C140">
-        <v>1</v>
-      </c>
-      <c r="D140" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>3</v>
-      </c>
-      <c r="B141">
-        <v>6</v>
-      </c>
-      <c r="C141">
-        <v>2</v>
-      </c>
-      <c r="D141" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>5</v>
-      </c>
-      <c r="B142">
-        <v>3</v>
-      </c>
-      <c r="C142">
-        <v>12</v>
-      </c>
-      <c r="D142" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>3</v>
-      </c>
-      <c r="B143">
-        <v>6</v>
-      </c>
-      <c r="C143">
-        <v>4</v>
-      </c>
-      <c r="D143" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>3</v>
-      </c>
-      <c r="B144">
-        <v>6</v>
-      </c>
       <c r="C144">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D144" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B145">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C145">
         <v>8</v>
       </c>
       <c r="D145" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B146">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C146">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D146" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
       <c r="A147" t="s">
         <v>3</v>
       </c>
       <c r="B147">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C147">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D147" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
       <c r="A148" t="s">
         <v>3</v>
       </c>
@@ -3214,13 +3334,13 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
       <c r="A149" t="s">
         <v>3</v>
       </c>
@@ -3228,41 +3348,41 @@
         <v>6</v>
       </c>
       <c r="C149">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D149" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B150">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C150">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D150" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B151">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C151">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D151" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
       <c r="A152" t="s">
         <v>3</v>
       </c>
@@ -3270,13 +3390,13 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D152" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
       <c r="A153" t="s">
         <v>3</v>
       </c>
@@ -3284,15 +3404,15 @@
         <v>6</v>
       </c>
       <c r="C153">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D153" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B154">
         <v>6</v>
@@ -3301,24 +3421,24 @@
         <v>8</v>
       </c>
       <c r="D154" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B155">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C155">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D155" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
       <c r="A156" t="s">
         <v>3</v>
       </c>
@@ -3326,1536 +3446,2082 @@
         <v>6</v>
       </c>
       <c r="C156">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D156" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B157">
         <v>6</v>
       </c>
       <c r="C157">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D157" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
       <c r="A158" t="s">
         <v>3</v>
       </c>
       <c r="B158">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C158">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D158" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
       <c r="A159" t="s">
         <v>3</v>
       </c>
       <c r="B159">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C159">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D159" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B160">
+        <v>6</v>
+      </c>
+      <c r="C160">
+        <v>14</v>
+      </c>
+      <c r="D160" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" t="s">
+        <v>5</v>
+      </c>
+      <c r="B161">
+        <v>3</v>
+      </c>
+      <c r="C161">
+        <v>23</v>
+      </c>
+      <c r="D161" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" t="s">
+        <v>3</v>
+      </c>
+      <c r="B162">
+        <v>6</v>
+      </c>
+      <c r="C162">
+        <v>17</v>
+      </c>
+      <c r="D162" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" t="s">
+        <v>3</v>
+      </c>
+      <c r="B163">
+        <v>6</v>
+      </c>
+      <c r="C163">
+        <v>19</v>
+      </c>
+      <c r="D163" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" t="s">
+        <v>3</v>
+      </c>
+      <c r="B164">
+        <v>6</v>
+      </c>
+      <c r="C164">
+        <v>20</v>
+      </c>
+      <c r="D164" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" t="s">
+        <v>7</v>
+      </c>
+      <c r="B165">
         <v>9</v>
-      </c>
-      <c r="C160">
-        <v>27</v>
-      </c>
-      <c r="D160" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>3</v>
-      </c>
-      <c r="B161">
-        <v>7</v>
-      </c>
-      <c r="C161">
-        <v>7</v>
-      </c>
-      <c r="D161" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>3</v>
-      </c>
-      <c r="B162">
-        <v>7</v>
-      </c>
-      <c r="C162">
-        <v>8</v>
-      </c>
-      <c r="D162" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>7</v>
-      </c>
-      <c r="B163">
-        <v>9</v>
-      </c>
-      <c r="C163">
-        <v>30</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>7</v>
-      </c>
-      <c r="B164">
-        <v>10</v>
-      </c>
-      <c r="C164">
-        <v>1</v>
-      </c>
-      <c r="D164" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>3</v>
-      </c>
-      <c r="B165">
-        <v>7</v>
       </c>
       <c r="C165">
         <v>10</v>
       </c>
       <c r="D165" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
       <c r="A166" t="s">
         <v>7</v>
       </c>
       <c r="B166">
+        <v>9</v>
+      </c>
+      <c r="C166">
+        <v>11</v>
+      </c>
+      <c r="D166" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" t="s">
+        <v>3</v>
+      </c>
+      <c r="B167">
+        <v>6</v>
+      </c>
+      <c r="C167">
+        <v>21</v>
+      </c>
+      <c r="D167" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" t="s">
+        <v>3</v>
+      </c>
+      <c r="B168">
+        <v>6</v>
+      </c>
+      <c r="C168">
+        <v>25</v>
+      </c>
+      <c r="D168" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" t="s">
+        <v>5</v>
+      </c>
+      <c r="B169">
+        <v>4</v>
+      </c>
+      <c r="C169">
+        <v>4</v>
+      </c>
+      <c r="D169" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" t="s">
+        <v>3</v>
+      </c>
+      <c r="B170">
+        <v>6</v>
+      </c>
+      <c r="C170">
+        <v>26</v>
+      </c>
+      <c r="D170" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" t="s">
+        <v>3</v>
+      </c>
+      <c r="B171">
+        <v>6</v>
+      </c>
+      <c r="C171">
+        <v>27</v>
+      </c>
+      <c r="D171" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" t="s">
+        <v>5</v>
+      </c>
+      <c r="B172">
+        <v>6</v>
+      </c>
+      <c r="C172">
+        <v>8</v>
+      </c>
+      <c r="D172" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" t="s">
+        <v>7</v>
+      </c>
+      <c r="B173">
+        <v>9</v>
+      </c>
+      <c r="C173">
+        <v>21</v>
+      </c>
+      <c r="D173" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" t="s">
+        <v>3</v>
+      </c>
+      <c r="B174">
+        <v>6</v>
+      </c>
+      <c r="C174">
+        <v>31</v>
+      </c>
+      <c r="D174" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" t="s">
+        <v>5</v>
+      </c>
+      <c r="B175">
+        <v>6</v>
+      </c>
+      <c r="C175">
         <v>10</v>
       </c>
-      <c r="C166">
+      <c r="D175" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" t="s">
+        <v>3</v>
+      </c>
+      <c r="B176">
+        <v>7</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+      <c r="D176" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" t="s">
+        <v>7</v>
+      </c>
+      <c r="B177">
+        <v>9</v>
+      </c>
+      <c r="C177">
+        <v>24</v>
+      </c>
+      <c r="D177" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" t="s">
+        <v>7</v>
+      </c>
+      <c r="B178">
+        <v>9</v>
+      </c>
+      <c r="C178">
+        <v>25</v>
+      </c>
+      <c r="D178" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" t="s">
+        <v>3</v>
+      </c>
+      <c r="B179">
+        <v>7</v>
+      </c>
+      <c r="C179">
         <v>4</v>
       </c>
-      <c r="D166" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>7</v>
-      </c>
-      <c r="B167">
+      <c r="D179" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" t="s">
+        <v>7</v>
+      </c>
+      <c r="B180">
+        <v>9</v>
+      </c>
+      <c r="C180">
+        <v>27</v>
+      </c>
+      <c r="D180" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" t="s">
+        <v>3</v>
+      </c>
+      <c r="B181">
+        <v>7</v>
+      </c>
+      <c r="C181">
+        <v>5</v>
+      </c>
+      <c r="D181" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" t="s">
+        <v>3</v>
+      </c>
+      <c r="B182">
+        <v>7</v>
+      </c>
+      <c r="C182">
+        <v>7</v>
+      </c>
+      <c r="D182" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" t="s">
+        <v>3</v>
+      </c>
+      <c r="B183">
+        <v>7</v>
+      </c>
+      <c r="C183">
+        <v>8</v>
+      </c>
+      <c r="D183" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" t="s">
+        <v>7</v>
+      </c>
+      <c r="B184">
+        <v>9</v>
+      </c>
+      <c r="C184">
+        <v>30</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" t="s">
+        <v>7</v>
+      </c>
+      <c r="B185">
         <v>10</v>
       </c>
-      <c r="C167">
-        <v>5</v>
-      </c>
-      <c r="D167" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>3</v>
-      </c>
-      <c r="B168">
-        <v>7</v>
-      </c>
-      <c r="C168">
+      <c r="C185">
+        <v>1</v>
+      </c>
+      <c r="D185" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" t="s">
+        <v>3</v>
+      </c>
+      <c r="B186">
+        <v>7</v>
+      </c>
+      <c r="C186">
+        <v>9</v>
+      </c>
+      <c r="D186" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" t="s">
+        <v>3</v>
+      </c>
+      <c r="B187">
+        <v>7</v>
+      </c>
+      <c r="C187">
+        <v>10</v>
+      </c>
+      <c r="D187" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" t="s">
+        <v>7</v>
+      </c>
+      <c r="B188">
+        <v>10</v>
+      </c>
+      <c r="C188">
+        <v>4</v>
+      </c>
+      <c r="D188" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" t="s">
+        <v>7</v>
+      </c>
+      <c r="B189">
+        <v>10</v>
+      </c>
+      <c r="C189">
+        <v>5</v>
+      </c>
+      <c r="D189" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" t="s">
+        <v>3</v>
+      </c>
+      <c r="B190">
+        <v>7</v>
+      </c>
+      <c r="C190">
+        <v>13</v>
+      </c>
+      <c r="D190" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" t="s">
+        <v>3</v>
+      </c>
+      <c r="B191">
+        <v>7</v>
+      </c>
+      <c r="C191">
         <v>14</v>
       </c>
-      <c r="D168" t="s">
+      <c r="D191" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" t="s">
+        <v>3</v>
+      </c>
+      <c r="B192">
+        <v>7</v>
+      </c>
+      <c r="C192">
+        <v>15</v>
+      </c>
+      <c r="D192" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" t="s">
+        <v>7</v>
+      </c>
+      <c r="B193">
+        <v>10</v>
+      </c>
+      <c r="C193">
+        <v>8</v>
+      </c>
+      <c r="D193" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>3</v>
-      </c>
-      <c r="B169">
-        <v>7</v>
-      </c>
-      <c r="C169">
+    <row r="194" spans="1:4">
+      <c r="A194" t="s">
+        <v>7</v>
+      </c>
+      <c r="B194">
+        <v>10</v>
+      </c>
+      <c r="C194">
+        <v>9</v>
+      </c>
+      <c r="D194" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" t="s">
+        <v>7</v>
+      </c>
+      <c r="B195">
+        <v>10</v>
+      </c>
+      <c r="C195">
+        <v>10</v>
+      </c>
+      <c r="D195" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" t="s">
+        <v>7</v>
+      </c>
+      <c r="B196">
+        <v>10</v>
+      </c>
+      <c r="C196">
+        <v>11</v>
+      </c>
+      <c r="D196" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" t="s">
+        <v>3</v>
+      </c>
+      <c r="B197">
+        <v>7</v>
+      </c>
+      <c r="C197">
+        <v>20</v>
+      </c>
+      <c r="D197" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" t="s">
+        <v>3</v>
+      </c>
+      <c r="B198">
+        <v>7</v>
+      </c>
+      <c r="C198">
+        <v>21</v>
+      </c>
+      <c r="D198" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" t="s">
+        <v>7</v>
+      </c>
+      <c r="B199">
+        <v>10</v>
+      </c>
+      <c r="C199">
+        <v>14</v>
+      </c>
+      <c r="D199" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" t="s">
+        <v>3</v>
+      </c>
+      <c r="B200">
+        <v>7</v>
+      </c>
+      <c r="C200">
+        <v>23</v>
+      </c>
+      <c r="D200" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" t="s">
+        <v>7</v>
+      </c>
+      <c r="B201">
+        <v>10</v>
+      </c>
+      <c r="C201">
+        <v>15</v>
+      </c>
+      <c r="D201" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" t="s">
+        <v>7</v>
+      </c>
+      <c r="B202">
+        <v>10</v>
+      </c>
+      <c r="C202">
         <v>16</v>
       </c>
-      <c r="D169" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>7</v>
-      </c>
-      <c r="B170">
+      <c r="D202" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" t="s">
+        <v>7</v>
+      </c>
+      <c r="B203">
         <v>10</v>
       </c>
-      <c r="C170">
-        <v>9</v>
-      </c>
-      <c r="D170" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>7</v>
-      </c>
-      <c r="B171">
+      <c r="C203">
+        <v>17</v>
+      </c>
+      <c r="D203" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" t="s">
+        <v>5</v>
+      </c>
+      <c r="B204">
+        <v>5</v>
+      </c>
+      <c r="C204">
+        <v>5</v>
+      </c>
+      <c r="D204" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" t="s">
+        <v>3</v>
+      </c>
+      <c r="B205">
+        <v>7</v>
+      </c>
+      <c r="C205">
+        <v>24</v>
+      </c>
+      <c r="D205" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" t="s">
+        <v>3</v>
+      </c>
+      <c r="B206">
+        <v>7</v>
+      </c>
+      <c r="C206">
+        <v>26</v>
+      </c>
+      <c r="D206" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" t="s">
+        <v>3</v>
+      </c>
+      <c r="B207">
+        <v>7</v>
+      </c>
+      <c r="C207">
+        <v>28</v>
+      </c>
+      <c r="D207" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" t="s">
+        <v>3</v>
+      </c>
+      <c r="B208">
+        <v>7</v>
+      </c>
+      <c r="C208">
+        <v>29</v>
+      </c>
+      <c r="D208" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" t="s">
+        <v>3</v>
+      </c>
+      <c r="B209">
+        <v>8</v>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="D209" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" t="s">
+        <v>3</v>
+      </c>
+      <c r="B210">
+        <v>8</v>
+      </c>
+      <c r="C210">
+        <v>4</v>
+      </c>
+      <c r="D210" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" t="s">
+        <v>3</v>
+      </c>
+      <c r="B211">
+        <v>8</v>
+      </c>
+      <c r="C211">
+        <v>5</v>
+      </c>
+      <c r="D211" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" t="s">
+        <v>3</v>
+      </c>
+      <c r="B212">
+        <v>8</v>
+      </c>
+      <c r="C212">
+        <v>7</v>
+      </c>
+      <c r="D212" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" t="s">
+        <v>3</v>
+      </c>
+      <c r="B213">
+        <v>8</v>
+      </c>
+      <c r="C213">
+        <v>8</v>
+      </c>
+      <c r="D213" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" t="s">
+        <v>3</v>
+      </c>
+      <c r="B214">
+        <v>8</v>
+      </c>
+      <c r="C214">
         <v>10</v>
       </c>
-      <c r="C171">
-        <v>10</v>
-      </c>
-      <c r="D171" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>7</v>
-      </c>
-      <c r="B172">
-        <v>10</v>
-      </c>
-      <c r="C172">
-        <v>11</v>
-      </c>
-      <c r="D172" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>3</v>
-      </c>
-      <c r="B173">
-        <v>7</v>
-      </c>
-      <c r="C173">
-        <v>20</v>
-      </c>
-      <c r="D173" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>3</v>
-      </c>
-      <c r="B174">
-        <v>7</v>
-      </c>
-      <c r="C174">
-        <v>21</v>
-      </c>
-      <c r="D174" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>7</v>
-      </c>
-      <c r="B175">
-        <v>10</v>
-      </c>
-      <c r="C175">
-        <v>14</v>
-      </c>
-      <c r="D175" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>7</v>
-      </c>
-      <c r="B176">
-        <v>10</v>
-      </c>
-      <c r="C176">
-        <v>15</v>
-      </c>
-      <c r="D176" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>7</v>
-      </c>
-      <c r="B177">
-        <v>10</v>
-      </c>
-      <c r="C177">
-        <v>16</v>
-      </c>
-      <c r="D177" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>7</v>
-      </c>
-      <c r="B178">
-        <v>10</v>
-      </c>
-      <c r="C178">
-        <v>17</v>
-      </c>
-      <c r="D178" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>5</v>
-      </c>
-      <c r="B179">
-        <v>5</v>
-      </c>
-      <c r="C179">
-        <v>5</v>
-      </c>
-      <c r="D179" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>3</v>
-      </c>
-      <c r="B180">
-        <v>7</v>
-      </c>
-      <c r="C180">
-        <v>26</v>
-      </c>
-      <c r="D180" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>3</v>
-      </c>
-      <c r="B181">
-        <v>7</v>
-      </c>
-      <c r="C181">
-        <v>28</v>
-      </c>
-      <c r="D181" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>3</v>
-      </c>
-      <c r="B182">
-        <v>7</v>
-      </c>
-      <c r="C182">
-        <v>29</v>
-      </c>
-      <c r="D182" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>3</v>
-      </c>
-      <c r="B183">
+      <c r="D214" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" t="s">
+        <v>3</v>
+      </c>
+      <c r="B215">
         <v>8</v>
-      </c>
-      <c r="C183">
-        <v>1</v>
-      </c>
-      <c r="D183" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>3</v>
-      </c>
-      <c r="B184">
-        <v>8</v>
-      </c>
-      <c r="C184">
-        <v>7</v>
-      </c>
-      <c r="D184" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>3</v>
-      </c>
-      <c r="B185">
-        <v>8</v>
-      </c>
-      <c r="C185">
-        <v>8</v>
-      </c>
-      <c r="D185" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>3</v>
-      </c>
-      <c r="B186">
-        <v>8</v>
-      </c>
-      <c r="C186">
-        <v>10</v>
-      </c>
-      <c r="D186" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>3</v>
-      </c>
-      <c r="B187">
-        <v>8</v>
-      </c>
-      <c r="C187">
-        <v>14</v>
-      </c>
-      <c r="D187" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>3</v>
-      </c>
-      <c r="B188">
-        <v>8</v>
-      </c>
-      <c r="C188">
-        <v>15</v>
-      </c>
-      <c r="D188" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>3</v>
-      </c>
-      <c r="B189">
-        <v>8</v>
-      </c>
-      <c r="C189">
-        <v>18</v>
-      </c>
-      <c r="D189" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>5</v>
-      </c>
-      <c r="B190">
-        <v>6</v>
-      </c>
-      <c r="C190">
-        <v>3</v>
-      </c>
-      <c r="D190" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>7</v>
-      </c>
-      <c r="B191">
-        <v>10</v>
-      </c>
-      <c r="C191">
-        <v>31</v>
-      </c>
-      <c r="D191" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>7</v>
-      </c>
-      <c r="B192">
-        <v>11</v>
-      </c>
-      <c r="C192">
-        <v>14</v>
-      </c>
-      <c r="D192" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>3</v>
-      </c>
-      <c r="B193">
-        <v>8</v>
-      </c>
-      <c r="C193">
-        <v>24</v>
-      </c>
-      <c r="D193" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>7</v>
-      </c>
-      <c r="B194">
-        <v>11</v>
-      </c>
-      <c r="C194">
-        <v>17</v>
-      </c>
-      <c r="D194" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>7</v>
-      </c>
-      <c r="B195">
-        <v>11</v>
-      </c>
-      <c r="C195">
-        <v>19</v>
-      </c>
-      <c r="D195" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>7</v>
-      </c>
-      <c r="B196">
-        <v>11</v>
-      </c>
-      <c r="C196">
-        <v>20</v>
-      </c>
-      <c r="D196" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>3</v>
-      </c>
-      <c r="B197">
-        <v>9</v>
-      </c>
-      <c r="C197">
-        <v>1</v>
-      </c>
-      <c r="D197" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>7</v>
-      </c>
-      <c r="B198">
-        <v>11</v>
-      </c>
-      <c r="C198">
-        <v>25</v>
-      </c>
-      <c r="D198" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>3</v>
-      </c>
-      <c r="B199">
-        <v>9</v>
-      </c>
-      <c r="C199">
-        <v>5</v>
-      </c>
-      <c r="D199" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>3</v>
-      </c>
-      <c r="B200">
-        <v>9</v>
-      </c>
-      <c r="C200">
-        <v>7</v>
-      </c>
-      <c r="D200" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>3</v>
-      </c>
-      <c r="B201">
-        <v>9</v>
-      </c>
-      <c r="C201">
-        <v>9</v>
-      </c>
-      <c r="D201" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>5</v>
-      </c>
-      <c r="B202">
-        <v>6</v>
-      </c>
-      <c r="C202">
-        <v>20</v>
-      </c>
-      <c r="D202" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>7</v>
-      </c>
-      <c r="B203">
-        <v>12</v>
-      </c>
-      <c r="C203">
-        <v>1</v>
-      </c>
-      <c r="D203" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>7</v>
-      </c>
-      <c r="B204">
-        <v>12</v>
-      </c>
-      <c r="C204">
-        <v>3</v>
-      </c>
-      <c r="D204" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>3</v>
-      </c>
-      <c r="B205">
-        <v>9</v>
-      </c>
-      <c r="C205">
-        <v>13</v>
-      </c>
-      <c r="D205" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>3</v>
-      </c>
-      <c r="B206">
-        <v>9</v>
-      </c>
-      <c r="C206">
-        <v>15</v>
-      </c>
-      <c r="D206" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>7</v>
-      </c>
-      <c r="B207">
-        <v>12</v>
-      </c>
-      <c r="C207">
-        <v>10</v>
-      </c>
-      <c r="D207" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>5</v>
-      </c>
-      <c r="B208">
-        <v>7</v>
-      </c>
-      <c r="C208">
-        <v>1</v>
-      </c>
-      <c r="D208" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>7</v>
-      </c>
-      <c r="B209">
-        <v>12</v>
-      </c>
-      <c r="C209">
-        <v>11</v>
-      </c>
-      <c r="D209" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>5</v>
-      </c>
-      <c r="B210">
-        <v>7</v>
-      </c>
-      <c r="C210">
-        <v>3</v>
-      </c>
-      <c r="D210" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>3</v>
-      </c>
-      <c r="B211">
-        <v>9</v>
-      </c>
-      <c r="C211">
-        <v>25</v>
-      </c>
-      <c r="D211" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>5</v>
-      </c>
-      <c r="B212">
-        <v>7</v>
-      </c>
-      <c r="C212">
-        <v>10</v>
-      </c>
-      <c r="D212" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>3</v>
-      </c>
-      <c r="B213">
-        <v>9</v>
-      </c>
-      <c r="C213">
-        <v>30</v>
-      </c>
-      <c r="D213" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>3</v>
-      </c>
-      <c r="B214">
-        <v>10</v>
-      </c>
-      <c r="C214">
-        <v>1</v>
-      </c>
-      <c r="D214" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>5</v>
-      </c>
-      <c r="B215">
-        <v>7</v>
       </c>
       <c r="C215">
         <v>13</v>
       </c>
       <c r="D215" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
       <c r="A216" t="s">
         <v>3</v>
       </c>
       <c r="B216">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C216">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D216" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B217">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C217">
         <v>15</v>
       </c>
       <c r="D217" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B218">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C218">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D218" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B219">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C219">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D219" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B220">
         <v>10</v>
       </c>
       <c r="C220">
+        <v>31</v>
+      </c>
+      <c r="D220" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" t="s">
+        <v>7</v>
+      </c>
+      <c r="B221">
+        <v>11</v>
+      </c>
+      <c r="C221">
+        <v>10</v>
+      </c>
+      <c r="D221" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" t="s">
+        <v>7</v>
+      </c>
+      <c r="B222">
+        <v>11</v>
+      </c>
+      <c r="C222">
+        <v>14</v>
+      </c>
+      <c r="D222" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" t="s">
+        <v>3</v>
+      </c>
+      <c r="B223">
         <v>8</v>
       </c>
-      <c r="D220" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>3</v>
-      </c>
-      <c r="B221">
-        <v>10</v>
-      </c>
-      <c r="C221">
-        <v>9</v>
-      </c>
-      <c r="D221" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>7</v>
-      </c>
-      <c r="B222">
-        <v>1</v>
-      </c>
-      <c r="C222">
-        <v>1</v>
-      </c>
-      <c r="D222" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>3</v>
-      </c>
-      <c r="B223">
-        <v>10</v>
-      </c>
       <c r="C223">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D223" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
       <c r="A224" t="s">
         <v>3</v>
       </c>
       <c r="B224">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C224">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D224" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B225">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C225">
         <v>25</v>
       </c>
       <c r="D225" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
       <c r="A226" t="s">
         <v>3</v>
       </c>
       <c r="B226">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C226">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D226" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B227">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C227">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D227" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B228">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C228">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D228" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B229">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C229">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D229" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B230">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C230">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D230" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B231">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C231">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D231" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B232">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C232">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B233">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C233">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D233" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B234">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C234">
         <v>4</v>
       </c>
       <c r="D234" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B235">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C235">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D235" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B236">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C236">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D236" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
       <c r="A237" t="s">
         <v>3</v>
       </c>
       <c r="B237">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C237">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D237" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
       <c r="A238" t="s">
         <v>3</v>
       </c>
       <c r="B238">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C238">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D238" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B239">
         <v>11</v>
       </c>
       <c r="C239">
-        <v>2</v>
-      </c>
-      <c r="D239" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B240">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C240">
+        <v>9</v>
+      </c>
+      <c r="D240" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
+        <v>5</v>
+      </c>
+      <c r="B241">
+        <v>6</v>
+      </c>
+      <c r="C241">
+        <v>20</v>
+      </c>
+      <c r="D241" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" t="s">
+        <v>7</v>
+      </c>
+      <c r="B242">
+        <v>12</v>
+      </c>
+      <c r="C242">
+        <v>1</v>
+      </c>
+      <c r="D242" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" t="s">
+        <v>7</v>
+      </c>
+      <c r="B243">
+        <v>12</v>
+      </c>
+      <c r="C243">
+        <v>3</v>
+      </c>
+      <c r="D243" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" t="s">
+        <v>3</v>
+      </c>
+      <c r="B244">
+        <v>9</v>
+      </c>
+      <c r="C244">
+        <v>13</v>
+      </c>
+      <c r="D244" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" t="s">
+        <v>3</v>
+      </c>
+      <c r="B245">
+        <v>9</v>
+      </c>
+      <c r="C245">
         <v>15</v>
       </c>
-      <c r="D240" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>3</v>
-      </c>
-      <c r="B241">
+      <c r="D245" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" t="s">
+        <v>7</v>
+      </c>
+      <c r="B246">
+        <v>12</v>
+      </c>
+      <c r="C246">
+        <v>10</v>
+      </c>
+      <c r="D246" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" t="s">
+        <v>5</v>
+      </c>
+      <c r="B247">
+        <v>7</v>
+      </c>
+      <c r="C247">
+        <v>1</v>
+      </c>
+      <c r="D247" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" t="s">
+        <v>7</v>
+      </c>
+      <c r="B248">
+        <v>12</v>
+      </c>
+      <c r="C248">
         <v>11</v>
       </c>
-      <c r="C241">
-        <v>6</v>
-      </c>
-      <c r="D241" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>3</v>
-      </c>
-      <c r="B242">
-        <v>11</v>
-      </c>
-      <c r="C242">
-        <v>10</v>
-      </c>
-      <c r="D242" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>3</v>
-      </c>
-      <c r="B243">
-        <v>11</v>
-      </c>
-      <c r="C243">
-        <v>12</v>
-      </c>
-      <c r="D243" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>3</v>
-      </c>
-      <c r="B244">
-        <v>11</v>
-      </c>
-      <c r="C244">
-        <v>15</v>
-      </c>
-      <c r="D244" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
-        <v>3</v>
-      </c>
-      <c r="B245">
-        <v>11</v>
-      </c>
-      <c r="C245">
-        <v>19</v>
-      </c>
-      <c r="D245" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
-        <v>3</v>
-      </c>
-      <c r="B246">
-        <v>11</v>
-      </c>
-      <c r="C246">
-        <v>22</v>
-      </c>
-      <c r="D246" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
-        <v>7</v>
-      </c>
-      <c r="B247">
-        <v>2</v>
-      </c>
-      <c r="C247">
-        <v>11</v>
-      </c>
-      <c r="D247" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
-        <v>7</v>
-      </c>
-      <c r="B248">
-        <v>2</v>
-      </c>
-      <c r="C248">
-        <v>14</v>
-      </c>
       <c r="D248" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B249">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C249">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D249" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B250">
         <v>9</v>
       </c>
       <c r="C250">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D250" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B251">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C251">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D251" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B252">
         <v>9</v>
       </c>
       <c r="C252">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D252" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B253">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C253">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
       <c r="A254" t="s">
         <v>5</v>
       </c>
       <c r="B254">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C254">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D254" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B255">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C255">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D255" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B256">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C256">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D256" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B257">
         <v>12</v>
       </c>
       <c r="C257">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D257" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
       <c r="A258" t="s">
         <v>3</v>
       </c>
       <c r="B258">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C258">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D258" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B259">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C259">
         <v>8</v>
       </c>
       <c r="D259" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B260">
         <v>10</v>
       </c>
       <c r="C260">
+        <v>9</v>
+      </c>
+      <c r="D260" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" t="s">
+        <v>7</v>
+      </c>
+      <c r="B261">
         <v>1</v>
       </c>
-      <c r="D260" t="s">
+      <c r="C261">
+        <v>1</v>
+      </c>
+      <c r="D261" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" t="s">
+        <v>3</v>
+      </c>
+      <c r="B262">
+        <v>10</v>
+      </c>
+      <c r="C262">
+        <v>12</v>
+      </c>
+      <c r="D262" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" t="s">
+        <v>3</v>
+      </c>
+      <c r="B263">
+        <v>10</v>
+      </c>
+      <c r="C263">
+        <v>13</v>
+      </c>
+      <c r="D263" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" t="s">
+        <v>5</v>
+      </c>
+      <c r="B264">
+        <v>7</v>
+      </c>
+      <c r="C264">
+        <v>25</v>
+      </c>
+      <c r="D264" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" t="s">
+        <v>3</v>
+      </c>
+      <c r="B265">
+        <v>10</v>
+      </c>
+      <c r="C265">
+        <v>15</v>
+      </c>
+      <c r="D265" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" t="s">
+        <v>3</v>
+      </c>
+      <c r="B266">
+        <v>10</v>
+      </c>
+      <c r="C266">
+        <v>16</v>
+      </c>
+      <c r="D266" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" t="s">
+        <v>3</v>
+      </c>
+      <c r="B267">
+        <v>10</v>
+      </c>
+      <c r="C267">
+        <v>18</v>
+      </c>
+      <c r="D267" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" t="s">
+        <v>3</v>
+      </c>
+      <c r="B268">
+        <v>10</v>
+      </c>
+      <c r="C268">
+        <v>19</v>
+      </c>
+      <c r="D268" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" t="s">
+        <v>3</v>
+      </c>
+      <c r="B269">
+        <v>10</v>
+      </c>
+      <c r="C269">
+        <v>20</v>
+      </c>
+      <c r="D269" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" t="s">
+        <v>5</v>
+      </c>
+      <c r="B270">
+        <v>7</v>
+      </c>
+      <c r="C270">
+        <v>27</v>
+      </c>
+      <c r="D270" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" t="s">
+        <v>5</v>
+      </c>
+      <c r="B271">
+        <v>8</v>
+      </c>
+      <c r="C271">
+        <v>3</v>
+      </c>
+      <c r="D271" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" t="s">
+        <v>3</v>
+      </c>
+      <c r="B272">
+        <v>10</v>
+      </c>
+      <c r="C272">
+        <v>23</v>
+      </c>
+      <c r="D272" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" t="s">
+        <v>5</v>
+      </c>
+      <c r="B273">
+        <v>8</v>
+      </c>
+      <c r="C273">
+        <v>4</v>
+      </c>
+      <c r="D273" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" t="s">
+        <v>5</v>
+      </c>
+      <c r="B274">
+        <v>8</v>
+      </c>
+      <c r="C274">
+        <v>5</v>
+      </c>
+      <c r="D274" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" t="s">
+        <v>5</v>
+      </c>
+      <c r="B275">
+        <v>8</v>
+      </c>
+      <c r="C275">
+        <v>11</v>
+      </c>
+      <c r="D275" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" t="s">
+        <v>3</v>
+      </c>
+      <c r="B276">
+        <v>10</v>
+      </c>
+      <c r="C276">
+        <v>30</v>
+      </c>
+      <c r="D276" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" t="s">
+        <v>3</v>
+      </c>
+      <c r="B277">
+        <v>11</v>
+      </c>
+      <c r="C277">
+        <v>1</v>
+      </c>
+      <c r="D277" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" t="s">
+        <v>3</v>
+      </c>
+      <c r="B278">
+        <v>11</v>
+      </c>
+      <c r="C278">
+        <v>2</v>
+      </c>
+      <c r="D278" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" t="s">
+        <v>5</v>
+      </c>
+      <c r="B279">
+        <v>8</v>
+      </c>
+      <c r="C279">
+        <v>15</v>
+      </c>
+      <c r="D279" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" t="s">
+        <v>3</v>
+      </c>
+      <c r="B280">
+        <v>11</v>
+      </c>
+      <c r="C280">
         <v>6</v>
       </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>5</v>
-      </c>
-      <c r="B261">
+      <c r="D280" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" t="s">
+        <v>3</v>
+      </c>
+      <c r="B281">
+        <v>11</v>
+      </c>
+      <c r="C281">
         <v>10</v>
       </c>
-      <c r="C261">
+      <c r="D281" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" t="s">
+        <v>3</v>
+      </c>
+      <c r="B282">
+        <v>11</v>
+      </c>
+      <c r="C282">
+        <v>12</v>
+      </c>
+      <c r="D282" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" t="s">
+        <v>3</v>
+      </c>
+      <c r="B283">
+        <v>11</v>
+      </c>
+      <c r="C283">
+        <v>15</v>
+      </c>
+      <c r="D283" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" t="s">
+        <v>3</v>
+      </c>
+      <c r="B284">
+        <v>11</v>
+      </c>
+      <c r="C284">
+        <v>19</v>
+      </c>
+      <c r="D284" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" t="s">
+        <v>3</v>
+      </c>
+      <c r="B285">
+        <v>11</v>
+      </c>
+      <c r="C285">
+        <v>22</v>
+      </c>
+      <c r="D285" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" t="s">
+        <v>7</v>
+      </c>
+      <c r="B286">
         <v>2</v>
       </c>
-      <c r="D261" t="s">
+      <c r="C286">
+        <v>11</v>
+      </c>
+      <c r="D286" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" t="s">
+        <v>7</v>
+      </c>
+      <c r="B287">
+        <v>2</v>
+      </c>
+      <c r="C287">
+        <v>14</v>
+      </c>
+      <c r="D287" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" t="s">
+        <v>3</v>
+      </c>
+      <c r="B288">
+        <v>11</v>
+      </c>
+      <c r="C288">
+        <v>29</v>
+      </c>
+      <c r="D288" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" t="s">
+        <v>5</v>
+      </c>
+      <c r="B289">
+        <v>9</v>
+      </c>
+      <c r="C289">
+        <v>15</v>
+      </c>
+      <c r="D289" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" t="s">
+        <v>3</v>
+      </c>
+      <c r="B290">
+        <v>12</v>
+      </c>
+      <c r="C290">
+        <v>5</v>
+      </c>
+      <c r="D290" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" t="s">
+        <v>5</v>
+      </c>
+      <c r="B291">
+        <v>9</v>
+      </c>
+      <c r="C291">
+        <v>18</v>
+      </c>
+      <c r="D291" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" t="s">
+        <v>5</v>
+      </c>
+      <c r="B292">
+        <v>9</v>
+      </c>
+      <c r="C292">
+        <v>19</v>
+      </c>
+      <c r="D292" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" t="s">
+        <v>5</v>
+      </c>
+      <c r="B293">
+        <v>9</v>
+      </c>
+      <c r="C293">
+        <v>21</v>
+      </c>
+      <c r="D293" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" t="s">
+        <v>5</v>
+      </c>
+      <c r="B294">
+        <v>9</v>
+      </c>
+      <c r="C294">
+        <v>22</v>
+      </c>
+      <c r="D294" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" t="s">
+        <v>3</v>
+      </c>
+      <c r="B295">
+        <v>12</v>
+      </c>
+      <c r="C295">
+        <v>7</v>
+      </c>
+      <c r="D295" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" t="s">
+        <v>3</v>
+      </c>
+      <c r="B296">
+        <v>12</v>
+      </c>
+      <c r="C296">
+        <v>9</v>
+      </c>
+      <c r="D296" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" t="s">
+        <v>3</v>
+      </c>
+      <c r="B297">
+        <v>12</v>
+      </c>
+      <c r="C297">
+        <v>15</v>
+      </c>
+      <c r="D297" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" t="s">
+        <v>7</v>
+      </c>
+      <c r="B298">
+        <v>3</v>
+      </c>
+      <c r="C298">
+        <v>8</v>
+      </c>
+      <c r="D298" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" t="s">
+        <v>5</v>
+      </c>
+      <c r="B299">
         <v>10</v>
       </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
-        <v>7</v>
-      </c>
-      <c r="B262">
-        <v>3</v>
-      </c>
-      <c r="C262">
+      <c r="C299">
+        <v>1</v>
+      </c>
+      <c r="D299" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" t="s">
+        <v>5</v>
+      </c>
+      <c r="B300">
+        <v>10</v>
+      </c>
+      <c r="C300">
+        <v>2</v>
+      </c>
+      <c r="D300" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" t="s">
+        <v>7</v>
+      </c>
+      <c r="B301">
+        <v>3</v>
+      </c>
+      <c r="C301">
         <v>14</v>
       </c>
-      <c r="D262" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>3</v>
-      </c>
-      <c r="B263">
+      <c r="D301" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" t="s">
+        <v>3</v>
+      </c>
+      <c r="B302">
         <v>12</v>
       </c>
-      <c r="C263">
+      <c r="C302">
         <v>25</v>
       </c>
-      <c r="D263" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
-        <v>3</v>
-      </c>
-      <c r="B264">
+      <c r="D302" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" t="s">
+        <v>3</v>
+      </c>
+      <c r="B303">
         <v>12</v>
       </c>
-      <c r="C264">
+      <c r="C303">
         <v>29</v>
       </c>
-      <c r="D264" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>7</v>
-      </c>
-      <c r="B265">
-        <v>3</v>
-      </c>
-      <c r="C265">
+      <c r="D303" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" t="s">
+        <v>7</v>
+      </c>
+      <c r="B304">
+        <v>3</v>
+      </c>
+      <c r="C304">
         <v>20</v>
       </c>
-      <c r="D265" t="s">
-        <v>198</v>
+      <c r="D304" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
